--- a/ai_logs/TruongHuynhAnhTuan_ai_log.xlsx
+++ b/ai_logs/TruongHuynhAnhTuan_ai_log.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thanh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C6ECCE-3D9E-4748-BC87-E238BAE811AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6410391-BD91-4E21-9A88-0F143E4EE27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ai_logs/TruongHuynhAnhTuan_ai_log.xlsx
+++ b/ai_logs/TruongHuynhAnhTuan_ai_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6410391-BD91-4E21-9A88-0F143E4EE27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128DAFAA-FBB2-4E73-8E4C-034A0CC5F4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -700,7 +700,9 @@
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="35" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="52.796875" customWidth="1"/>
+    <col min="3" max="6" width="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="22.8" x14ac:dyDescent="0.4">

--- a/ai_logs/TruongHuynhAnhTuan_ai_log.xlsx
+++ b/ai_logs/TruongHuynhAnhTuan_ai_log.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thanh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFE56FA-8851-4B7A-BEB8-430C02FFB8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1191FE-BC3F-4296-8E53-B336C9BF6F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -734,9 +734,6 @@
     <t>Test với format ngày khác bị lỗi parse</t>
   </si>
   <si>
-    <t>Thêm try-catch và định dạng chuẩn ISO</t>
-  </si>
-  <si>
     <t>False Execution Claim</t>
   </si>
   <si>
@@ -762,6 +759,9 @@
   </si>
   <si>
     <t>Tự viết logic đồng bộ trong BookingController.</t>
+  </si>
+  <si>
+    <t>Thêm try-catch và định dạng chuẩn ISO.</t>
   </si>
 </sst>
 </file>
@@ -952,20 +952,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1281,7 +1281,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -1300,7 +1300,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1308,7 +1308,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1316,7 +1316,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1324,7 +1324,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -1519,7 +1519,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="20"/>
@@ -1531,7 +1531,7 @@
       <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="20"/>
@@ -2170,7 +2170,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="20"/>
@@ -2180,7 +2180,7 @@
       <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="19" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="20"/>
@@ -2256,7 +2256,7 @@
         <v>231</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2264,19 +2264,19 @@
         <v>21</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>236</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2507,7 +2507,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="20"/>
@@ -2515,7 +2515,7 @@
       <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>79</v>
       </c>
       <c r="B2" s="20"/>

--- a/ai_logs/TruongHuynhAnhTuan_ai_log.xlsx
+++ b/ai_logs/TruongHuynhAnhTuan_ai_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thanh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31F5A3D-D76F-445A-808B-47FD8FD9F0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CBD936-85EE-4523-826D-DF8DB86BC79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -641,9 +641,6 @@
     <t>“trim la sao”</t>
   </si>
   <si>
-    <t>AI giải thích trim() loại bỏ khoảng trắng</t>
-  </si>
-  <si>
     <t>Biết cần trim input để tránh lỗi</t>
   </si>
   <si>
@@ -792,6 +789,9 @@
   </si>
   <si>
     <t>Phản hồi lại AI để viết lại script test với dải ghế động giả lập độc lập, đảm bảo ghế trống luôn có sẵn để đo lường chính xác tỷ lệ tranh chấp.</t>
+  </si>
+  <si>
+    <t>AI giải thích trim() loại bỏ khoảng trắng.</t>
   </si>
 </sst>
 </file>
@@ -982,18 +982,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1311,7 +1311,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -1330,7 +1330,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1338,7 +1338,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1346,7 +1346,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1354,7 +1354,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -1383,7 +1383,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>10</v>
@@ -1432,16 +1432,16 @@
     </row>
     <row r="18" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1549,7 +1549,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="20"/>
@@ -1561,7 +1561,7 @@
       <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="19" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="20"/>
@@ -1618,7 +1618,7 @@
         <v>110</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>111</v>
@@ -1644,7 +1644,7 @@
         <v>115</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>116</v>
@@ -1670,7 +1670,7 @@
         <v>120</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>121</v>
@@ -1696,7 +1696,7 @@
         <v>124</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>125</v>
@@ -1722,7 +1722,7 @@
         <v>128</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>129</v>
@@ -1748,7 +1748,7 @@
         <v>132</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>133</v>
@@ -1774,7 +1774,7 @@
         <v>136</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>137</v>
@@ -1800,7 +1800,7 @@
         <v>140</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>141</v>
@@ -1826,7 +1826,7 @@
         <v>144</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>145</v>
@@ -1852,7 +1852,7 @@
         <v>149</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>150</v>
@@ -1878,7 +1878,7 @@
         <v>153</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>154</v>
@@ -1904,7 +1904,7 @@
         <v>157</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>161</v>
@@ -1930,7 +1930,7 @@
         <v>160</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>162</v>
@@ -1956,7 +1956,7 @@
         <v>165</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>150</v>
@@ -1982,7 +1982,7 @@
         <v>168</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>169</v>
@@ -2008,7 +2008,7 @@
         <v>172</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>173</v>
@@ -2161,13 +2161,13 @@
         <v>200</v>
       </c>
       <c r="F25" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="H25" s="7" t="s">
         <v>202</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2178,22 +2178,22 @@
         <v>146</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="E26" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="F26" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="G26" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="H26" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2216,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>47</v>
       </c>
       <c r="B1" s="20"/>
@@ -2226,7 +2226,7 @@
       <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>48</v>
       </c>
       <c r="B2" s="20"/>
@@ -2260,19 +2260,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2293,16 +2293,16 @@
         <v>62</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>227</v>
-      </c>
       <c r="F6" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2310,19 +2310,19 @@
         <v>21</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>231</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2330,19 +2330,19 @@
         <v>23</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2565,7 +2565,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="20"/>
